--- a/WebManage/public/file/Trạm 2_2021-11-01_2021-11-07.xlsx
+++ b/WebManage/public/file/Trạm 2_2021-11-01_2021-11-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Mã trạm</t>
   </si>
@@ -68,12 +68,6 @@
   </si>
   <si>
     <t>75BCD15</t>
-  </si>
-  <si>
-    <t>1/11/2021 21:18:00</t>
-  </si>
-  <si>
-    <t>1/11/2021 22:2:00</t>
   </si>
   <si>
     <t>1/11/2021 22:59:00</t>
@@ -456,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="17" width="10" customWidth="1"/>
@@ -523,49 +517,49 @@
         <v>18</v>
       </c>
       <c r="C2">
-        <v>1635776325</v>
+        <v>1635782365</v>
       </c>
       <c r="D2">
-        <v>24.3808</v>
+        <v>24.8735</v>
       </c>
       <c r="E2">
-        <v>25.2482</v>
+        <v>25.9958</v>
       </c>
       <c r="F2">
-        <v>30.1895</v>
+        <v>34.9862</v>
       </c>
       <c r="G2">
-        <v>22.7037</v>
+        <v>23.9563</v>
       </c>
       <c r="H2">
-        <v>88.9327</v>
+        <v>89.4343</v>
       </c>
       <c r="I2">
-        <v>101893</v>
+        <v>101869</v>
       </c>
       <c r="J2">
-        <v>56</v>
+        <v>522</v>
       </c>
       <c r="K2">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="L2">
+        <v>36</v>
+      </c>
+      <c r="M2">
+        <v>13</v>
+      </c>
+      <c r="N2">
         <v>45</v>
       </c>
-      <c r="M2">
-        <v>78</v>
-      </c>
-      <c r="N2">
-        <v>62</v>
-      </c>
       <c r="O2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="P2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="Q2">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -576,154 +570,48 @@
         <v>19</v>
       </c>
       <c r="C3">
-        <v>1635778965</v>
+        <v>1635993818</v>
       </c>
       <c r="D3">
-        <v>21.9565</v>
+        <v>23.8026</v>
       </c>
       <c r="E3">
-        <v>28.026</v>
+        <v>24.0694</v>
       </c>
       <c r="F3">
-        <v>34.6486</v>
+        <v>34.4756</v>
       </c>
       <c r="G3">
-        <v>22.6131</v>
+        <v>22.2407</v>
       </c>
       <c r="H3">
-        <v>88.7288</v>
+        <v>88.1165</v>
       </c>
       <c r="I3">
-        <v>101815</v>
+        <v>101891</v>
       </c>
       <c r="J3">
-        <v>4753</v>
+        <v>22</v>
       </c>
       <c r="K3">
-        <v>96</v>
+        <v>226</v>
       </c>
       <c r="L3">
-        <v>485</v>
+        <v>78</v>
       </c>
       <c r="M3">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="N3">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="O3">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="P3">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="Q3">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4">
-        <v>1635782365</v>
-      </c>
-      <c r="D4">
-        <v>24.8735</v>
-      </c>
-      <c r="E4">
-        <v>25.9958</v>
-      </c>
-      <c r="F4">
-        <v>34.9862</v>
-      </c>
-      <c r="G4">
-        <v>23.9563</v>
-      </c>
-      <c r="H4">
-        <v>89.4343</v>
-      </c>
-      <c r="I4">
-        <v>101869</v>
-      </c>
-      <c r="J4">
-        <v>522</v>
-      </c>
-      <c r="K4">
-        <v>36</v>
-      </c>
-      <c r="L4">
-        <v>36</v>
-      </c>
-      <c r="M4">
-        <v>13</v>
-      </c>
-      <c r="N4">
-        <v>45</v>
-      </c>
-      <c r="O4">
-        <v>12</v>
-      </c>
-      <c r="P4">
-        <v>23</v>
-      </c>
-      <c r="Q4">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5">
-        <v>1635993818</v>
-      </c>
-      <c r="D5">
-        <v>23.8026</v>
-      </c>
-      <c r="E5">
-        <v>24.0694</v>
-      </c>
-      <c r="F5">
-        <v>34.4756</v>
-      </c>
-      <c r="G5">
-        <v>22.2407</v>
-      </c>
-      <c r="H5">
-        <v>88.1165</v>
-      </c>
-      <c r="I5">
-        <v>101891</v>
-      </c>
-      <c r="J5">
-        <v>22</v>
-      </c>
-      <c r="K5">
-        <v>226</v>
-      </c>
-      <c r="L5">
-        <v>78</v>
-      </c>
-      <c r="M5">
-        <v>36</v>
-      </c>
-      <c r="N5">
-        <v>98</v>
-      </c>
-      <c r="O5">
-        <v>12</v>
-      </c>
-      <c r="P5">
-        <v>78</v>
-      </c>
-      <c r="Q5">
         <v>45</v>
       </c>
     </row>
